--- a/data/countries.xlsx
+++ b/data/countries.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B746C74-D8C6-465A-8573-3867731A7311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2370C147-9CF5-44C9-A29B-DA45E6E70B77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3000" yWindow="3000" windowWidth="28800" windowHeight="15410" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -434,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S121"/>
+  <dimension ref="A1:S133"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.1796875" style="4" bestFit="1" customWidth="1"/>
@@ -1992,6 +1992,69 @@
     <row r="121" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A121" s="4">
         <v>45992</v>
+      </c>
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A122" s="4">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A123" s="4">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A124" s="4">
+        <v>46082</v>
+      </c>
+      <c r="E124" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A125" s="4">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A126" s="4">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A127" s="4">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A128" s="4">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A129" s="4">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A130" s="4">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A131" s="4">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A132" s="4">
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A133" s="4">
+        <v>46357</v>
       </c>
     </row>
   </sheetData>
@@ -2019,6 +2082,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002D4181E9E5D52F4C9586F49BFE5EE298" ma:contentTypeVersion="" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8a7a4b3985722b9877beb0be694fbd58">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="1071F304-F5D9-4CC4-AFCF-D37DA46A96D4" xmlns:ns3="d92fc194-eb53-4f7a-b45f-993e54cb3c65" xmlns:ns4="f191ad30-9ade-4f0c-b78e-cf30469879ae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="751d83e966f247b9feaf745e5d14cfa5" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -2209,15 +2281,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0ECEC803-CE3A-41AA-8A6B-E3884C13B2B5}">
   <ds:schemaRefs>
@@ -2238,6 +2301,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77A77888-53C6-464C-8A2C-8B68487BDD80}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CDF0CD2-A3B5-41A6-B6D3-1EA02F2B6377}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2256,12 +2327,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77A77888-53C6-464C-8A2C-8B68487BDD80}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/countries.xlsx
+++ b/data/countries.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2370C147-9CF5-44C9-A29B-DA45E6E70B77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3F4A925-5FB2-4B13-8857-5873240204E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3000" yWindow="3000" windowWidth="28800" windowHeight="15410" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -435,24 +435,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S133"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.1796875" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="3.26953125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="8.26953125" style="2" customWidth="1"/>
-    <col min="15" max="15" width="11.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.1796875" style="2"/>
+    <col min="10" max="10" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="8.28515625" style="2" customWidth="1"/>
+    <col min="15" max="15" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>10</v>
       </c>
@@ -502,7 +502,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>42370</v>
       </c>
@@ -510,17 +510,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>42401</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>42430</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>42461</v>
       </c>
@@ -537,7 +537,7 @@
       </c>
       <c r="P5" s="3"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>42491</v>
       </c>
@@ -557,7 +557,7 @@
       </c>
       <c r="P6" s="3"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>42522</v>
       </c>
@@ -574,7 +574,7 @@
       </c>
       <c r="P7" s="3"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>42552</v>
       </c>
@@ -597,7 +597,7 @@
       </c>
       <c r="P8" s="3"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>42583</v>
       </c>
@@ -617,7 +617,7 @@
       </c>
       <c r="P9" s="3"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>42614</v>
       </c>
@@ -634,7 +634,7 @@
       </c>
       <c r="P10" s="3"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>42644</v>
       </c>
@@ -651,7 +651,7 @@
       </c>
       <c r="P11" s="3"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>42675</v>
       </c>
@@ -674,7 +674,7 @@
       </c>
       <c r="P12" s="3"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>42705</v>
       </c>
@@ -697,7 +697,7 @@
         <v>54.641111111111108</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>42736</v>
       </c>
@@ -717,7 +717,7 @@
       </c>
       <c r="P14" s="3"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>42767</v>
       </c>
@@ -734,7 +734,7 @@
       </c>
       <c r="P15" s="3"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>42795</v>
       </c>
@@ -751,7 +751,7 @@
       </c>
       <c r="P16" s="3"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>42826</v>
       </c>
@@ -768,7 +768,7 @@
       </c>
       <c r="P17" s="3"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>42856</v>
       </c>
@@ -791,7 +791,7 @@
       </c>
       <c r="P18" s="3"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>42887</v>
       </c>
@@ -811,7 +811,7 @@
       </c>
       <c r="P19" s="3"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>42917</v>
       </c>
@@ -831,7 +831,7 @@
       </c>
       <c r="P20" s="3"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>42948</v>
       </c>
@@ -850,7 +850,7 @@
       </c>
       <c r="P21" s="3"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>42979</v>
       </c>
@@ -870,7 +870,7 @@
       </c>
       <c r="P22" s="3"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>43009</v>
       </c>
@@ -893,7 +893,7 @@
       </c>
       <c r="P23" s="3"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>43040</v>
       </c>
@@ -913,7 +913,7 @@
       </c>
       <c r="P24" s="3"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>43070</v>
       </c>
@@ -936,7 +936,7 @@
         <v>50.095833333333331</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>43101</v>
       </c>
@@ -956,7 +956,7 @@
       </c>
       <c r="P26" s="3"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>43132</v>
       </c>
@@ -973,7 +973,7 @@
       </c>
       <c r="P27" s="3"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>43160</v>
       </c>
@@ -996,7 +996,7 @@
       </c>
       <c r="P28" s="3"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>43191</v>
       </c>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P29" s="3"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>43221</v>
       </c>
@@ -1021,7 +1021,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>43252</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>126.33</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>43282</v>
       </c>
@@ -1043,7 +1043,7 @@
         <v>68.010000000000005</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>43313</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>43344</v>
       </c>
@@ -1059,7 +1059,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>43374</v>
       </c>
@@ -1073,7 +1073,7 @@
         <v>81.7</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>43405</v>
       </c>
@@ -1084,7 +1084,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>43435</v>
       </c>
@@ -1096,7 +1096,7 @@
         <v>48.080000000000005</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>43466</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>43497</v>
       </c>
@@ -1115,7 +1115,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>43525</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>43556</v>
       </c>
@@ -1137,7 +1137,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>43586</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>43617</v>
       </c>
@@ -1165,7 +1165,7 @@
         <v>89.8</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>43647</v>
       </c>
@@ -1182,7 +1182,7 @@
         <v>101.03</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>43678</v>
       </c>
@@ -1190,7 +1190,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>43709</v>
       </c>
@@ -1198,7 +1198,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>43739</v>
       </c>
@@ -1209,7 +1209,7 @@
         <v>105.25</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>43770</v>
       </c>
@@ -1223,7 +1223,7 @@
         <v>122.22</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>43800</v>
       </c>
@@ -1235,7 +1235,7 @@
         <v>54.81666666666667</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>43831</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>43862</v>
       </c>
@@ -1254,7 +1254,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <v>43891</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
         <v>43922</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
         <v>43952</v>
       </c>
@@ -1281,7 +1281,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>43983</v>
       </c>
@@ -1289,7 +1289,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
         <v>44013</v>
       </c>
@@ -1297,7 +1297,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
         <v>44044</v>
       </c>
@@ -1305,7 +1305,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
         <v>44075</v>
       </c>
@@ -1313,7 +1313,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
         <v>44105</v>
       </c>
@@ -1321,7 +1321,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
         <v>44136</v>
       </c>
@@ -1329,7 +1329,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
         <v>44166</v>
       </c>
@@ -1341,7 +1341,7 @@
         <v>24.041666666666668</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
         <v>44197</v>
       </c>
@@ -1349,7 +1349,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
         <v>44228</v>
       </c>
@@ -1357,52 +1357,52 @@
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
         <v>44256</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
         <v>44287</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
         <v>44317</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
         <v>44348</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="4">
         <v>44378</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
         <v>44409</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
         <v>44440</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
         <v>44470</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="4">
         <v>44501</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
         <v>44531</v>
       </c>
@@ -1410,12 +1410,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="4">
         <v>44562</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="4">
         <v>44593</v>
       </c>
@@ -1423,22 +1423,22 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="4">
         <v>44621</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
         <v>44652</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
         <v>44682</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
         <v>44713</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="4">
         <v>44743</v>
       </c>
@@ -1454,7 +1454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A81" s="4">
         <v>44774</v>
       </c>
@@ -1462,7 +1462,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A82" s="4">
         <v>44805</v>
       </c>
@@ -1470,7 +1470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A83" s="4">
         <v>44835</v>
       </c>
@@ -1478,7 +1478,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A84" s="4">
         <v>44866</v>
       </c>
@@ -1496,7 +1496,7 @@
       <c r="R84" s="3"/>
       <c r="S84" s="3"/>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A85" s="4">
         <v>44896</v>
       </c>
@@ -1514,7 +1514,7 @@
       <c r="R85" s="3"/>
       <c r="S85" s="3"/>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A86" s="4">
         <v>44927</v>
       </c>
@@ -1532,7 +1532,7 @@
       <c r="R86" s="3"/>
       <c r="S86" s="3"/>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A87" s="4">
         <v>44958</v>
       </c>
@@ -1553,7 +1553,7 @@
       <c r="R87" s="3"/>
       <c r="S87" s="3"/>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A88" s="4">
         <v>44986</v>
       </c>
@@ -1573,7 +1573,7 @@
       <c r="R88" s="3"/>
       <c r="S88" s="3"/>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A89" s="4">
         <v>45017</v>
       </c>
@@ -1593,7 +1593,7 @@
       <c r="R89" s="3"/>
       <c r="S89" s="3"/>
     </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A90" s="4">
         <v>45047</v>
       </c>
@@ -1611,7 +1611,7 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
     </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A91" s="4">
         <v>45078</v>
       </c>
@@ -1629,7 +1629,7 @@
       <c r="R91" s="3"/>
       <c r="S91" s="3"/>
     </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A92" s="4">
         <v>45108</v>
       </c>
@@ -1647,7 +1647,7 @@
       <c r="R92" s="3"/>
       <c r="S92" s="3"/>
     </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A93" s="4">
         <v>45139</v>
       </c>
@@ -1669,7 +1669,7 @@
       <c r="R93" s="3"/>
       <c r="S93" s="3"/>
     </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A94" s="4">
         <v>45170</v>
       </c>
@@ -1687,7 +1687,7 @@
       <c r="R94" s="3"/>
       <c r="S94" s="3"/>
     </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A95" s="4">
         <v>45200</v>
       </c>
@@ -1705,7 +1705,7 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
     </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A96" s="4">
         <v>45231</v>
       </c>
@@ -1725,7 +1725,7 @@
       <c r="R96" s="3"/>
       <c r="S96" s="3"/>
     </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A97" s="4">
         <v>45261</v>
       </c>
@@ -1743,7 +1743,7 @@
       <c r="R97" s="3"/>
       <c r="S97" s="3"/>
     </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A98" s="4">
         <v>45292</v>
       </c>
@@ -1761,7 +1761,7 @@
       <c r="R98" s="3"/>
       <c r="S98" s="3"/>
     </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A99" s="4">
         <v>45323</v>
       </c>
@@ -1779,7 +1779,7 @@
       <c r="R99" s="3"/>
       <c r="S99" s="3"/>
     </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A100" s="4">
         <v>45352</v>
       </c>
@@ -1797,7 +1797,7 @@
       <c r="R100" s="3"/>
       <c r="S100" s="3"/>
     </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A101" s="4">
         <v>45383</v>
       </c>
@@ -1819,7 +1819,7 @@
       <c r="R101" s="3"/>
       <c r="S101" s="3"/>
     </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A102" s="4">
         <v>45413</v>
       </c>
@@ -1839,7 +1839,7 @@
       <c r="R102" s="3"/>
       <c r="S102" s="3"/>
     </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A103" s="4">
         <v>45444</v>
       </c>
@@ -1864,7 +1864,7 @@
       <c r="R103" s="3"/>
       <c r="S103" s="3"/>
     </row>
-    <row r="104" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A104" s="4">
         <v>45474</v>
       </c>
@@ -1882,12 +1882,12 @@
       <c r="R104" s="3"/>
       <c r="S104" s="3"/>
     </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A105" s="4">
         <v>45505</v>
       </c>
     </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A106" s="4">
         <v>45536</v>
       </c>
@@ -1895,7 +1895,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A107" s="4">
         <v>45566</v>
       </c>
@@ -1903,17 +1903,17 @@
         <v>8</v>
       </c>
     </row>
-    <row r="108" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A108" s="4">
         <v>45597</v>
       </c>
     </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A109" s="4">
         <v>45627</v>
       </c>
     </row>
-    <row r="110" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A110" s="4">
         <v>45658</v>
       </c>
@@ -1921,17 +1921,17 @@
         <v>3</v>
       </c>
     </row>
-    <row r="111" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A111" s="4">
         <v>45689</v>
       </c>
     </row>
-    <row r="112" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A112" s="4">
         <v>45717</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A113" s="4">
         <v>45748</v>
       </c>
@@ -1942,7 +1942,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114" s="4">
         <v>45778</v>
       </c>
@@ -1950,22 +1950,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A115" s="4">
         <v>45809</v>
       </c>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A116" s="4">
         <v>45839</v>
       </c>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A117" s="4">
         <v>45870</v>
       </c>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A118" s="4">
         <v>45901</v>
       </c>
@@ -1973,7 +1973,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A119" s="4">
         <v>45931</v>
       </c>
@@ -1981,7 +1981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A120" s="4">
         <v>45962</v>
       </c>
@@ -1989,70 +1989,73 @@
         <v>3</v>
       </c>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A121" s="4">
         <v>45992</v>
       </c>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A122" s="4">
         <v>46023</v>
       </c>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A123" s="4">
         <v>46054</v>
       </c>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A124" s="4">
         <v>46082</v>
       </c>
       <c r="E124" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+      <c r="I124" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A125" s="4">
         <v>46113</v>
       </c>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A126" s="4">
         <v>46143</v>
       </c>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A127" s="4">
         <v>46174</v>
       </c>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A128" s="4">
         <v>46204</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" s="4">
         <v>46235</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" s="4">
         <v>46266</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" s="4">
         <v>46296</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" s="4">
         <v>46327</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" s="4">
         <v>46357</v>
       </c>
@@ -2082,15 +2085,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002D4181E9E5D52F4C9586F49BFE5EE298" ma:contentTypeVersion="" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8a7a4b3985722b9877beb0be694fbd58">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="1071F304-F5D9-4CC4-AFCF-D37DA46A96D4" xmlns:ns3="d92fc194-eb53-4f7a-b45f-993e54cb3c65" xmlns:ns4="f191ad30-9ade-4f0c-b78e-cf30469879ae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="751d83e966f247b9feaf745e5d14cfa5" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -2281,6 +2275,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0ECEC803-CE3A-41AA-8A6B-E3884C13B2B5}">
   <ds:schemaRefs>
@@ -2301,14 +2304,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77A77888-53C6-464C-8A2C-8B68487BDD80}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CDF0CD2-A3B5-41A6-B6D3-1EA02F2B6377}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2327,4 +2322,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77A77888-53C6-464C-8A2C-8B68487BDD80}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/countries.xlsx
+++ b/data/countries.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3F4A925-5FB2-4B13-8857-5873240204E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C969027-1E52-4690-A012-9D0369037E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4140" yWindow="4140" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -435,24 +435,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S133"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="3.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1796875" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.26953125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.453125" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.26953125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="8.28515625" style="2" customWidth="1"/>
-    <col min="15" max="15" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="2"/>
+    <col min="10" max="10" width="8.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="8.26953125" style="2" customWidth="1"/>
+    <col min="15" max="15" width="11.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.1796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>10</v>
       </c>
@@ -502,7 +502,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
         <v>42370</v>
       </c>
@@ -510,17 +510,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
         <v>42401</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
         <v>42430</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
         <v>42461</v>
       </c>
@@ -537,7 +537,7 @@
       </c>
       <c r="P5" s="3"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
         <v>42491</v>
       </c>
@@ -557,7 +557,7 @@
       </c>
       <c r="P6" s="3"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
         <v>42522</v>
       </c>
@@ -574,7 +574,7 @@
       </c>
       <c r="P7" s="3"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
         <v>42552</v>
       </c>
@@ -597,7 +597,7 @@
       </c>
       <c r="P8" s="3"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
         <v>42583</v>
       </c>
@@ -617,7 +617,7 @@
       </c>
       <c r="P9" s="3"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
         <v>42614</v>
       </c>
@@ -634,7 +634,7 @@
       </c>
       <c r="P10" s="3"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
         <v>42644</v>
       </c>
@@ -651,7 +651,7 @@
       </c>
       <c r="P11" s="3"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" s="4">
         <v>42675</v>
       </c>
@@ -674,7 +674,7 @@
       </c>
       <c r="P12" s="3"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
         <v>42705</v>
       </c>
@@ -697,7 +697,7 @@
         <v>54.641111111111108</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
         <v>42736</v>
       </c>
@@ -717,7 +717,7 @@
       </c>
       <c r="P14" s="3"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
         <v>42767</v>
       </c>
@@ -734,7 +734,7 @@
       </c>
       <c r="P15" s="3"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" s="4">
         <v>42795</v>
       </c>
@@ -751,7 +751,7 @@
       </c>
       <c r="P16" s="3"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17" s="4">
         <v>42826</v>
       </c>
@@ -768,7 +768,7 @@
       </c>
       <c r="P17" s="3"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18" s="4">
         <v>42856</v>
       </c>
@@ -791,7 +791,7 @@
       </c>
       <c r="P18" s="3"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A19" s="4">
         <v>42887</v>
       </c>
@@ -811,7 +811,7 @@
       </c>
       <c r="P19" s="3"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A20" s="4">
         <v>42917</v>
       </c>
@@ -831,7 +831,7 @@
       </c>
       <c r="P20" s="3"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21" s="4">
         <v>42948</v>
       </c>
@@ -850,7 +850,7 @@
       </c>
       <c r="P21" s="3"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22" s="4">
         <v>42979</v>
       </c>
@@ -870,7 +870,7 @@
       </c>
       <c r="P22" s="3"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23" s="4">
         <v>43009</v>
       </c>
@@ -893,7 +893,7 @@
       </c>
       <c r="P23" s="3"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A24" s="4">
         <v>43040</v>
       </c>
@@ -913,7 +913,7 @@
       </c>
       <c r="P24" s="3"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A25" s="4">
         <v>43070</v>
       </c>
@@ -936,7 +936,7 @@
         <v>50.095833333333331</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A26" s="4">
         <v>43101</v>
       </c>
@@ -956,7 +956,7 @@
       </c>
       <c r="P26" s="3"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A27" s="4">
         <v>43132</v>
       </c>
@@ -973,7 +973,7 @@
       </c>
       <c r="P27" s="3"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A28" s="4">
         <v>43160</v>
       </c>
@@ -996,7 +996,7 @@
       </c>
       <c r="P28" s="3"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A29" s="4">
         <v>43191</v>
       </c>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P29" s="3"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A30" s="4">
         <v>43221</v>
       </c>
@@ -1021,7 +1021,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A31" s="4">
         <v>43252</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>126.33</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A32" s="4">
         <v>43282</v>
       </c>
@@ -1043,7 +1043,7 @@
         <v>68.010000000000005</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A33" s="4">
         <v>43313</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A34" s="4">
         <v>43344</v>
       </c>
@@ -1059,7 +1059,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A35" s="4">
         <v>43374</v>
       </c>
@@ -1073,7 +1073,7 @@
         <v>81.7</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A36" s="4">
         <v>43405</v>
       </c>
@@ -1084,7 +1084,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A37" s="4">
         <v>43435</v>
       </c>
@@ -1096,7 +1096,7 @@
         <v>48.080000000000005</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A38" s="4">
         <v>43466</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A39" s="4">
         <v>43497</v>
       </c>
@@ -1115,7 +1115,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A40" s="4">
         <v>43525</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A41" s="4">
         <v>43556</v>
       </c>
@@ -1137,7 +1137,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A42" s="4">
         <v>43586</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A43" s="4">
         <v>43617</v>
       </c>
@@ -1165,7 +1165,7 @@
         <v>89.8</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A44" s="4">
         <v>43647</v>
       </c>
@@ -1182,7 +1182,7 @@
         <v>101.03</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A45" s="4">
         <v>43678</v>
       </c>
@@ -1190,7 +1190,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A46" s="4">
         <v>43709</v>
       </c>
@@ -1198,7 +1198,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A47" s="4">
         <v>43739</v>
       </c>
@@ -1209,7 +1209,7 @@
         <v>105.25</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A48" s="4">
         <v>43770</v>
       </c>
@@ -1223,7 +1223,7 @@
         <v>122.22</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A49" s="4">
         <v>43800</v>
       </c>
@@ -1235,7 +1235,7 @@
         <v>54.81666666666667</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A50" s="4">
         <v>43831</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A51" s="4">
         <v>43862</v>
       </c>
@@ -1254,7 +1254,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A52" s="4">
         <v>43891</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A53" s="4">
         <v>43922</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A54" s="4">
         <v>43952</v>
       </c>
@@ -1281,7 +1281,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A55" s="4">
         <v>43983</v>
       </c>
@@ -1289,7 +1289,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A56" s="4">
         <v>44013</v>
       </c>
@@ -1297,7 +1297,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A57" s="4">
         <v>44044</v>
       </c>
@@ -1305,7 +1305,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A58" s="4">
         <v>44075</v>
       </c>
@@ -1313,7 +1313,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A59" s="4">
         <v>44105</v>
       </c>
@@ -1321,7 +1321,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A60" s="4">
         <v>44136</v>
       </c>
@@ -1329,7 +1329,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A61" s="4">
         <v>44166</v>
       </c>
@@ -1341,7 +1341,7 @@
         <v>24.041666666666668</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A62" s="4">
         <v>44197</v>
       </c>
@@ -1349,7 +1349,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A63" s="4">
         <v>44228</v>
       </c>
@@ -1357,52 +1357,52 @@
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A64" s="4">
         <v>44256</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A65" s="4">
         <v>44287</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A66" s="4">
         <v>44317</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A67" s="4">
         <v>44348</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A68" s="4">
         <v>44378</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A69" s="4">
         <v>44409</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A70" s="4">
         <v>44440</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A71" s="4">
         <v>44470</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A72" s="4">
         <v>44501</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A73" s="4">
         <v>44531</v>
       </c>
@@ -1410,12 +1410,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A74" s="4">
         <v>44562</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A75" s="4">
         <v>44593</v>
       </c>
@@ -1423,22 +1423,22 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A76" s="4">
         <v>44621</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A77" s="4">
         <v>44652</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A78" s="4">
         <v>44682</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A79" s="4">
         <v>44713</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A80" s="4">
         <v>44743</v>
       </c>
@@ -1454,7 +1454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A81" s="4">
         <v>44774</v>
       </c>
@@ -1462,7 +1462,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A82" s="4">
         <v>44805</v>
       </c>
@@ -1470,7 +1470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A83" s="4">
         <v>44835</v>
       </c>
@@ -1478,7 +1478,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A84" s="4">
         <v>44866</v>
       </c>
@@ -1496,7 +1496,7 @@
       <c r="R84" s="3"/>
       <c r="S84" s="3"/>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A85" s="4">
         <v>44896</v>
       </c>
@@ -1514,7 +1514,7 @@
       <c r="R85" s="3"/>
       <c r="S85" s="3"/>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A86" s="4">
         <v>44927</v>
       </c>
@@ -1532,7 +1532,7 @@
       <c r="R86" s="3"/>
       <c r="S86" s="3"/>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A87" s="4">
         <v>44958</v>
       </c>
@@ -1553,7 +1553,7 @@
       <c r="R87" s="3"/>
       <c r="S87" s="3"/>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A88" s="4">
         <v>44986</v>
       </c>
@@ -1573,7 +1573,7 @@
       <c r="R88" s="3"/>
       <c r="S88" s="3"/>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A89" s="4">
         <v>45017</v>
       </c>
@@ -1593,7 +1593,7 @@
       <c r="R89" s="3"/>
       <c r="S89" s="3"/>
     </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A90" s="4">
         <v>45047</v>
       </c>
@@ -1611,7 +1611,7 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
     </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A91" s="4">
         <v>45078</v>
       </c>
@@ -1629,7 +1629,7 @@
       <c r="R91" s="3"/>
       <c r="S91" s="3"/>
     </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A92" s="4">
         <v>45108</v>
       </c>
@@ -1647,7 +1647,7 @@
       <c r="R92" s="3"/>
       <c r="S92" s="3"/>
     </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A93" s="4">
         <v>45139</v>
       </c>
@@ -1669,7 +1669,7 @@
       <c r="R93" s="3"/>
       <c r="S93" s="3"/>
     </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A94" s="4">
         <v>45170</v>
       </c>
@@ -1687,7 +1687,7 @@
       <c r="R94" s="3"/>
       <c r="S94" s="3"/>
     </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A95" s="4">
         <v>45200</v>
       </c>
@@ -1705,7 +1705,7 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
     </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A96" s="4">
         <v>45231</v>
       </c>
@@ -1725,7 +1725,7 @@
       <c r="R96" s="3"/>
       <c r="S96" s="3"/>
     </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A97" s="4">
         <v>45261</v>
       </c>
@@ -1743,7 +1743,7 @@
       <c r="R97" s="3"/>
       <c r="S97" s="3"/>
     </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A98" s="4">
         <v>45292</v>
       </c>
@@ -1761,7 +1761,7 @@
       <c r="R98" s="3"/>
       <c r="S98" s="3"/>
     </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A99" s="4">
         <v>45323</v>
       </c>
@@ -1779,7 +1779,7 @@
       <c r="R99" s="3"/>
       <c r="S99" s="3"/>
     </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A100" s="4">
         <v>45352</v>
       </c>
@@ -1797,7 +1797,7 @@
       <c r="R100" s="3"/>
       <c r="S100" s="3"/>
     </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A101" s="4">
         <v>45383</v>
       </c>
@@ -1819,7 +1819,7 @@
       <c r="R101" s="3"/>
       <c r="S101" s="3"/>
     </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A102" s="4">
         <v>45413</v>
       </c>
@@ -1839,7 +1839,7 @@
       <c r="R102" s="3"/>
       <c r="S102" s="3"/>
     </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A103" s="4">
         <v>45444</v>
       </c>
@@ -1864,7 +1864,7 @@
       <c r="R103" s="3"/>
       <c r="S103" s="3"/>
     </row>
-    <row r="104" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A104" s="4">
         <v>45474</v>
       </c>
@@ -1882,12 +1882,12 @@
       <c r="R104" s="3"/>
       <c r="S104" s="3"/>
     </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A105" s="4">
         <v>45505</v>
       </c>
     </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A106" s="4">
         <v>45536</v>
       </c>
@@ -1895,7 +1895,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A107" s="4">
         <v>45566</v>
       </c>
@@ -1903,17 +1903,17 @@
         <v>8</v>
       </c>
     </row>
-    <row r="108" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A108" s="4">
         <v>45597</v>
       </c>
     </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A109" s="4">
         <v>45627</v>
       </c>
     </row>
-    <row r="110" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A110" s="4">
         <v>45658</v>
       </c>
@@ -1921,17 +1921,17 @@
         <v>3</v>
       </c>
     </row>
-    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A111" s="4">
         <v>45689</v>
       </c>
     </row>
-    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A112" s="4">
         <v>45717</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A113" s="4">
         <v>45748</v>
       </c>
@@ -1942,7 +1942,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A114" s="4">
         <v>45778</v>
       </c>
@@ -1950,22 +1950,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A115" s="4">
         <v>45809</v>
       </c>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A116" s="4">
         <v>45839</v>
       </c>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A117" s="4">
         <v>45870</v>
       </c>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A118" s="4">
         <v>45901</v>
       </c>
@@ -1973,7 +1973,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A119" s="4">
         <v>45931</v>
       </c>
@@ -1981,7 +1981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A120" s="4">
         <v>45962</v>
       </c>
@@ -1989,22 +1989,22 @@
         <v>3</v>
       </c>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A121" s="4">
         <v>45992</v>
       </c>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A122" s="4">
         <v>46023</v>
       </c>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A123" s="4">
         <v>46054</v>
       </c>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A124" s="4">
         <v>46082</v>
       </c>
@@ -2015,47 +2015,50 @@
         <v>4</v>
       </c>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A125" s="4">
         <v>46113</v>
       </c>
-    </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C125" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A126" s="4">
         <v>46143</v>
       </c>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A127" s="4">
         <v>46174</v>
       </c>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A128" s="4">
         <v>46204</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A129" s="4">
         <v>46235</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A130" s="4">
         <v>46266</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A131" s="4">
         <v>46296</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A132" s="4">
         <v>46327</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A133" s="4">
         <v>46357</v>
       </c>
@@ -2070,21 +2073,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <FileSizeOrChildItemCount xmlns="d92fc194-eb53-4f7a-b45f-993e54cb3c65">17 KB</FileSizeOrChildItemCount>
-    <_dlc_ExpireDate xmlns="http://schemas.microsoft.com/sharepoint/v3">2028-11-30T23:00:00+00:00</_dlc_ExpireDate>
-    <TaxCatchAll xmlns="f191ad30-9ade-4f0c-b78e-cf30469879ae"/>
-    <DocumentType xmlns="1071F304-F5D9-4CC4-AFCF-D37DA46A96D4">1</DocumentType>
-    <TaxKeywordTaxHTField xmlns="d92fc194-eb53-4f7a-b45f-993e54cb3c65">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </TaxKeywordTaxHTField>
-    <_dlc_ExpireDateSaved xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002D4181E9E5D52F4C9586F49BFE5EE298" ma:contentTypeVersion="" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8a7a4b3985722b9877beb0be694fbd58">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="1071F304-F5D9-4CC4-AFCF-D37DA46A96D4" xmlns:ns3="d92fc194-eb53-4f7a-b45f-993e54cb3c65" xmlns:ns4="f191ad30-9ade-4f0c-b78e-cf30469879ae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="751d83e966f247b9feaf745e5d14cfa5" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -2275,6 +2263,21 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <FileSizeOrChildItemCount xmlns="d92fc194-eb53-4f7a-b45f-993e54cb3c65">17 KB</FileSizeOrChildItemCount>
+    <_dlc_ExpireDate xmlns="http://schemas.microsoft.com/sharepoint/v3">2028-11-30T23:00:00+00:00</_dlc_ExpireDate>
+    <TaxCatchAll xmlns="f191ad30-9ade-4f0c-b78e-cf30469879ae"/>
+    <DocumentType xmlns="1071F304-F5D9-4CC4-AFCF-D37DA46A96D4">1</DocumentType>
+    <TaxKeywordTaxHTField xmlns="d92fc194-eb53-4f7a-b45f-993e54cb3c65">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </TaxKeywordTaxHTField>
+    <_dlc_ExpireDateSaved xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -2285,25 +2288,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0ECEC803-CE3A-41AA-8A6B-E3884C13B2B5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="f191ad30-9ade-4f0c-b78e-cf30469879ae"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="d92fc194-eb53-4f7a-b45f-993e54cb3c65"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="1071F304-F5D9-4CC4-AFCF-D37DA46A96D4"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CDF0CD2-A3B5-41A6-B6D3-1EA02F2B6377}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2324,6 +2308,25 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0ECEC803-CE3A-41AA-8A6B-E3884C13B2B5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="f191ad30-9ade-4f0c-b78e-cf30469879ae"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="d92fc194-eb53-4f7a-b45f-993e54cb3c65"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="1071F304-F5D9-4CC4-AFCF-D37DA46A96D4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77A77888-53C6-464C-8A2C-8B68487BDD80}">
   <ds:schemaRefs>

--- a/data/countries.xlsx
+++ b/data/countries.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C969027-1E52-4690-A012-9D0369037E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B72F1D84-885E-452F-AE18-81AED09D963D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="4140" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2027,6 +2027,9 @@
       <c r="A126" s="4">
         <v>46143</v>
       </c>
+      <c r="E126" s="3">
+        <v>3</v>
+      </c>
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A127" s="4">
@@ -2264,6 +2267,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <FileSizeOrChildItemCount xmlns="d92fc194-eb53-4f7a-b45f-993e54cb3c65">17 KB</FileSizeOrChildItemCount>
@@ -2276,15 +2288,6 @@
     <_dlc_ExpireDateSaved xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2309,6 +2312,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77A77888-53C6-464C-8A2C-8B68487BDD80}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0ECEC803-CE3A-41AA-8A6B-E3884C13B2B5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -2325,12 +2336,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77A77888-53C6-464C-8A2C-8B68487BDD80}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>